--- a/data/trans_orig/P23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>251896</t>
+          <t>253188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295887</t>
+          <t>297708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>261321</t>
+          <t>262182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301176</t>
+          <t>301957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531411</t>
+          <t>529089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587749</t>
+          <t>590343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>65322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161073</t>
+          <t>160504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203333</t>
+          <t>204298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125974</t>
+          <t>124377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164243</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295465</t>
+          <t>294443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353733</t>
+          <t>353081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>271748</t>
+          <t>267930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>322553</t>
+          <t>323950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>295688</t>
+          <t>294665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>346883</t>
+          <t>344806</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>579500</t>
+          <t>578845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>653978</t>
+          <t>653148</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56419</t>
+          <t>55907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88717</t>
+          <t>88081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91923</t>
+          <t>91043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130315</t>
+          <t>132338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29812</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56034</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>349283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>401803</t>
+          <t>405373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191646</t>
+          <t>192044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239356</t>
+          <t>239408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>553114</t>
+          <t>553197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>627826</t>
+          <t>627853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186478</t>
+          <t>188588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234056</t>
+          <t>237180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337246</t>
+          <t>333701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>390723</t>
+          <t>391104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>540164</t>
+          <t>541694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>611577</t>
+          <t>613730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69587</t>
+          <t>68030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103428</t>
+          <t>102941</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>51534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84937</t>
+          <t>84697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130322</t>
+          <t>130587</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178384</t>
+          <t>178465</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32459</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32161</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>295951</t>
+          <t>295817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347225</t>
+          <t>346185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211598</t>
+          <t>210575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263850</t>
+          <t>262648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>521561</t>
+          <t>521801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>591968</t>
+          <t>589797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136255</t>
+          <t>137225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179643</t>
+          <t>179636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285904</t>
+          <t>284190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331188</t>
+          <t>330748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>434548</t>
+          <t>435216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>498001</t>
+          <t>498472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105659</t>
+          <t>107810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146831</t>
+          <t>146628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48484</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>77310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164504</t>
+          <t>164074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216687</t>
+          <t>212398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209355</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255624</t>
+          <t>255190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111579</t>
+          <t>110362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150063</t>
+          <t>149329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>330498</t>
+          <t>331086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>394463</t>
+          <t>391943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109458</t>
+          <t>108772</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146545</t>
+          <t>145412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322961</t>
+          <t>321647</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>352176</t>
+          <t>352123</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>437271</t>
+          <t>439489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>494782</t>
+          <t>495467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111638</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148809</t>
+          <t>148814</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125954</t>
+          <t>127219</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170638</t>
+          <t>171763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,39 +3249,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7186</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7201</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>107268</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>143153</t>
+          <t>142111</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>59652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>144853</t>
+          <t>144998</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194011</t>
+          <t>191879</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133786</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>312642</t>
+          <t>311517</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329712</t>
+          <t>329546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>418676</t>
+          <t>416561</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>461433</t>
+          <t>462098</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107315</t>
+          <t>106987</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138966</t>
+          <t>139285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>117693</t>
+          <t>114927</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155814</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38724</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>62734</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>70048</t>
+          <t>70518</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>309420</t>
+          <t>308919</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>326210</t>
+          <t>326749</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>370072</t>
+          <t>372548</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>412683</t>
+          <t>414313</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>100262</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>128977</t>
+          <t>127843</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>105490</t>
+          <t>104100</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>143417</t>
+          <t>143388</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>821</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29307</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1200076</t>
+          <t>1203141</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1310485</t>
+          <t>1316105</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2203911</t>
+          <t>2202130</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2311143</t>
+          <t>2308664</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3434762</t>
+          <t>3439197</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3594076</t>
+          <t>3600392</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>588377</t>
+          <t>584210</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>674870</t>
+          <t>674534</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>228119</t>
+          <t>227951</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>286169</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>831236</t>
+          <t>831198</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>939946</t>
+          <t>939920</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>68275</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>102893</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>147719</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>196882</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1243869</t>
+          <t>1246038</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1358298</t>
+          <t>1358779</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>734097</t>
+          <t>734624</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>832959</t>
+          <t>826978</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2004640</t>
+          <t>2001220</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2158558</t>
+          <t>2163486</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246860</t>
+          <t>248299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290310</t>
+          <t>290731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>240615</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>280954</t>
+          <t>281776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>502995</t>
+          <t>501363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>562039</t>
+          <t>562519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27692</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,82 +5760,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17782</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27262</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>42105</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>30831</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>55143</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17782</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9970</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27562</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>42105</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>31707</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>55693</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123360</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161633</t>
+          <t>160191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113151</t>
+          <t>112553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151196</t>
+          <t>149974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247130</t>
+          <t>244899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303324</t>
+          <t>300533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239367</t>
+          <t>238938</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291428</t>
+          <t>289314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>250269</t>
+          <t>247955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300041</t>
+          <t>298289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>500887</t>
+          <t>502629</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>574203</t>
+          <t>576810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93414</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>69458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104573</t>
+          <t>103096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137294</t>
+          <t>137381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185600</t>
+          <t>186136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>42594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>36703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70751</t>
+          <t>72102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>293037</t>
+          <t>291098</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344363</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203175</t>
+          <t>202059</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251719</t>
+          <t>250448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>507482</t>
+          <t>509364</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>581960</t>
+          <t>584494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218607</t>
+          <t>216386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269004</t>
+          <t>266800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307800</t>
+          <t>309544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362913</t>
+          <t>362418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>539517</t>
+          <t>541445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>615688</t>
+          <t>615224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93797</t>
+          <t>94873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133787</t>
+          <t>133934</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107178</t>
+          <t>105722</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>148369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212900</t>
+          <t>213838</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>272481</t>
+          <t>272327</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283125</t>
+          <t>281897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334647</t>
+          <t>334013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210627</t>
+          <t>208523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261485</t>
+          <t>261086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508465</t>
+          <t>506940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>581174</t>
+          <t>581604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139504</t>
+          <t>140197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>184208</t>
+          <t>187900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253066</t>
+          <t>254725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>307195</t>
+          <t>309644</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>408259</t>
+          <t>410153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479794</t>
+          <t>480350</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198982</t>
+          <t>197671</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>112491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233241</t>
+          <t>234001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297043</t>
+          <t>294247</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19876</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>42778</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>241626</t>
+          <t>240266</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296756</t>
+          <t>292516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198790</t>
+          <t>198649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250738</t>
+          <t>251523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>454288</t>
+          <t>454448</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>529276</t>
+          <t>526539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106690</t>
+          <t>106733</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145860</t>
+          <t>145692</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307964</t>
+          <t>305950</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>345159</t>
+          <t>345704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>422010</t>
+          <t>421613</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>484904</t>
+          <t>483644</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126611</t>
+          <t>128776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168017</t>
+          <t>170455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>67986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175962</t>
+          <t>174351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228443</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>130925</t>
+          <t>129967</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>172503</t>
+          <t>171538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>83503</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>189053</t>
+          <t>187956</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>242208</t>
+          <t>244043</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72906</t>
+          <t>71922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105694</t>
+          <t>104320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>311059</t>
+          <t>311170</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>333937</t>
+          <t>333435</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>386894</t>
+          <t>384111</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>437533</t>
+          <t>437488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153346</t>
+          <t>152647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189803</t>
+          <t>189128</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157277</t>
+          <t>158499</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>205447</t>
+          <t>208469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>29571</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51327</t>
+          <t>51746</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>88329</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>96321</t>
+          <t>95177</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>368806</t>
+          <t>369265</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>383794</t>
+          <t>383883</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>434075</t>
+          <t>429745</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>480632</t>
+          <t>478348</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>126525</t>
+          <t>126285</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>160462</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>128750</t>
+          <t>129989</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>173380</t>
+          <t>174166</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9194,62 +9194,62 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>12609</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>13405</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40033</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1169218</t>
+          <t>1174886</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1285685</t>
+          <t>1295126</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2123877</t>
+          <t>2127896</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2246418</t>
+          <t>2245641</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3322320</t>
+          <t>3339155</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3501530</t>
+          <t>3508414</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>783459</t>
+          <t>787449</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>893771</t>
+          <t>889698</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>356331</t>
+          <t>355637</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>430372</t>
+          <t>430250</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1169229</t>
+          <t>1170752</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1298826</t>
+          <t>1299146</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>76477</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>119316</t>
+          <t>116998</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>94330</t>
+          <t>91729</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>144947</t>
+          <t>145511</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>199703</t>
+          <t>199524</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1201751</t>
+          <t>1208657</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1322573</t>
+          <t>1318921</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>848762</t>
+          <t>846545</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>958163</t>
+          <t>954179</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2080245</t>
+          <t>2085102</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2251549</t>
+          <t>2241909</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>242974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281999</t>
+          <t>283132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>250249</t>
+          <t>250559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285602</t>
+          <t>285880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>503454</t>
+          <t>505041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>558541</t>
+          <t>559899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114331</t>
+          <t>113466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153252</t>
+          <t>153022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>79196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111402</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203509</t>
+          <t>201733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257002</t>
+          <t>255364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247118</t>
+          <t>246305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295871</t>
+          <t>294501</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>265158</t>
+          <t>263586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309075</t>
+          <t>309540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>527059</t>
+          <t>528553</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>591825</t>
+          <t>593573</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>64347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>75882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91452</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132196</t>
+          <t>128575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40658</t>
+          <t>40844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69013</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215413</t>
+          <t>215339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>265292</t>
+          <t>262885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169817</t>
+          <t>168796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>213067</t>
+          <t>213330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>396546</t>
+          <t>398895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>462515</t>
+          <t>462144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289876</t>
+          <t>288958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>342064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>312772</t>
+          <t>316182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364363</t>
+          <t>366497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620462</t>
+          <t>617319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692525</t>
+          <t>691344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11529,12 +11529,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103517</t>
+          <t>104063</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81317</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118800</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159349</t>
+          <t>160919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>213501</t>
+          <t>212332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>44238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>221461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274146</t>
+          <t>273694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187564</t>
+          <t>184908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234913</t>
+          <t>233602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420998</t>
+          <t>420379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>494912</t>
+          <t>490413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211363</t>
+          <t>213682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261244</t>
+          <t>262412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288332</t>
+          <t>290819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341772</t>
+          <t>339346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>512781</t>
+          <t>516523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>586839</t>
+          <t>590369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111072</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155131</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82840</t>
+          <t>82721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122779</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>204517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261649</t>
+          <t>261660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36536</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244297</t>
+          <t>241423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296445</t>
+          <t>295637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>193504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241546</t>
+          <t>239615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>452296</t>
+          <t>448616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526976</t>
+          <t>520140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148163</t>
+          <t>148631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192225</t>
+          <t>193751</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287913</t>
+          <t>290860</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333333</t>
+          <t>335220</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448167</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>515010</t>
+          <t>516207</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139555</t>
+          <t>139370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181454</t>
+          <t>180395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>53524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87112</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202559</t>
+          <t>199570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259153</t>
+          <t>257241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26787</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>118099</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>159792</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>88031</t>
+          <t>89478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216047</t>
+          <t>218898</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>275038</t>
+          <t>273471</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -13151,12 +13151,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116547</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153011</t>
+          <t>152263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>300848</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>328767</t>
+          <t>330712</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>422702</t>
+          <t>422968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>474183</t>
+          <t>476280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124558</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>158895</t>
+          <t>159711</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>45285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151553</t>
+          <t>151316</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>196677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -13377,12 +13377,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65014</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>93945</t>
+          <t>96774</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -13720,12 +13720,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95557</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>123837</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>376740</t>
+          <t>375845</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>392498</t>
+          <t>393109</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13770,12 +13770,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>474628</t>
+          <t>474401</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>517273</t>
+          <t>516957</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13805,12 +13805,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13833,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>108086</t>
+          <t>107838</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>135935</t>
+          <t>135255</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>108119</t>
+          <t>106505</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>145873</t>
+          <t>144497</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14109,12 +14109,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1441327</t>
+          <t>1442904</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1558000</t>
+          <t>1559712</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2163871</t>
+          <t>2173783</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2283319</t>
+          <t>2285609</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3646002</t>
+          <t>3647684</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3815399</t>
+          <t>3820062</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>652111</t>
+          <t>654103</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>748100</t>
+          <t>747566</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1028560</t>
+          <t>1022622</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1148926</t>
+          <t>1149943</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>113295</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>141584</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>196425</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1040643</t>
+          <t>1038811</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1154044</t>
+          <t>1152918</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>801808</t>
+          <t>797859</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>902935</t>
+          <t>901243</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1867999</t>
+          <t>1866753</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2024678</t>
+          <t>2020665</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253188</t>
+          <t>251888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297708</t>
+          <t>296102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262182</t>
+          <t>263509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301957</t>
+          <t>302519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>529089</t>
+          <t>530594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590343</t>
+          <t>590865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>34922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37715</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160504</t>
+          <t>159365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>204620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>124882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>163686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294443</t>
+          <t>294538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353081</t>
+          <t>354875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>270528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323950</t>
+          <t>326070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>294804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>344806</t>
+          <t>346248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>578845</t>
+          <t>581992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>653148</t>
+          <t>656455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>56268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88081</t>
+          <t>88446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132338</t>
+          <t>132711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,47 +1542,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19792</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12320</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30080</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19792</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12556</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>32208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>59204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>349283</t>
+          <t>346416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>405373</t>
+          <t>402448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>192044</t>
+          <t>189288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239408</t>
+          <t>239766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>553197</t>
+          <t>551484</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>627853</t>
+          <t>625242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188588</t>
+          <t>186040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237180</t>
+          <t>235776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333701</t>
+          <t>337661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391104</t>
+          <t>392312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541694</t>
+          <t>540217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613730</t>
+          <t>616536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68030</t>
+          <t>69525</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102941</t>
+          <t>105112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51534</t>
+          <t>54089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84697</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130587</t>
+          <t>132231</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178465</t>
+          <t>180212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>33093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>29244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56744</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>295817</t>
+          <t>296042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346185</t>
+          <t>350082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210575</t>
+          <t>211312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>262648</t>
+          <t>262250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>521801</t>
+          <t>519672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589797</t>
+          <t>592312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137225</t>
+          <t>137007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179636</t>
+          <t>178690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284190</t>
+          <t>285784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>330748</t>
+          <t>331048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>435216</t>
+          <t>436904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>498472</t>
+          <t>499011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107810</t>
+          <t>106272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146628</t>
+          <t>146564</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48715</t>
+          <t>48501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77310</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164074</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>212398</t>
+          <t>212920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>28097</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>207080</t>
+          <t>209205</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255190</t>
+          <t>253915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110362</t>
+          <t>111683</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149329</t>
+          <t>150882</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331086</t>
+          <t>332298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391943</t>
+          <t>395674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108772</t>
+          <t>109721</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145412</t>
+          <t>145557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>321647</t>
+          <t>323330</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>352123</t>
+          <t>353911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>439489</t>
+          <t>441808</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>495467</t>
+          <t>495884</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111159</t>
+          <t>112295</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148814</t>
+          <t>149745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127219</t>
+          <t>124362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171763</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>104338</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142111</t>
+          <t>140506</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>32570</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59652</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>146368</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>191879</t>
+          <t>191121</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99832</t>
+          <t>101587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133174</t>
+          <t>134892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>311517</t>
+          <t>312600</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329546</t>
+          <t>330253</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>416561</t>
+          <t>416268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>462098</t>
+          <t>459921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106987</t>
+          <t>105192</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>139285</t>
+          <t>138552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114927</t>
+          <t>117341</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>154104</t>
+          <t>160188</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>62160</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>43694</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>70518</t>
+          <t>71503</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>60978</t>
+          <t>62195</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>89347</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>308919</t>
+          <t>310201</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>326749</t>
+          <t>326182</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>372548</t>
+          <t>373371</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>414313</t>
+          <t>414581</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>99166</t>
+          <t>98988</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>127843</t>
+          <t>126692</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>104100</t>
+          <t>103604</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>143388</t>
+          <t>142706</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>33791</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1203141</t>
+          <t>1205655</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1316105</t>
+          <t>1315444</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2202130</t>
+          <t>2206620</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2308664</t>
+          <t>2314695</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3439197</t>
+          <t>3434129</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3600392</t>
+          <t>3602434</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>584210</t>
+          <t>582012</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>674534</t>
+          <t>674906</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>227951</t>
+          <t>226717</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>289190</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>831198</t>
+          <t>837182</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>939920</t>
+          <t>943162</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>70808</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>106217</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>143237</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1246038</t>
+          <t>1244689</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1358779</t>
+          <t>1356023</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>733772</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>826978</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2001220</t>
+          <t>2007914</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2163486</t>
+          <t>2158918</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>249828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290731</t>
+          <t>291696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242348</t>
+          <t>240731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281776</t>
+          <t>282128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>501363</t>
+          <t>500356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>562519</t>
+          <t>559382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49595</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35845</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>55277</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121044</t>
+          <t>121077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160191</t>
+          <t>161845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112553</t>
+          <t>112666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149974</t>
+          <t>150169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244899</t>
+          <t>245213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300533</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238938</t>
+          <t>241973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289314</t>
+          <t>291265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247955</t>
+          <t>250106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>298289</t>
+          <t>300951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>502629</t>
+          <t>505392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>576810</t>
+          <t>577878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>89796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69458</t>
+          <t>71062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103096</t>
+          <t>106486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137381</t>
+          <t>136501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186136</t>
+          <t>183299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42594</t>
+          <t>44531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36703</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>39924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>72646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>291098</t>
+          <t>291876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>344776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>202059</t>
+          <t>202717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250448</t>
+          <t>249514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>509364</t>
+          <t>506434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>584494</t>
+          <t>576768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216386</t>
+          <t>216351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266800</t>
+          <t>268269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309544</t>
+          <t>310186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362418</t>
+          <t>362841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541445</t>
+          <t>541847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>615224</t>
+          <t>616633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94873</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133934</t>
+          <t>133333</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105722</t>
+          <t>106991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>148369</t>
+          <t>148944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>213838</t>
+          <t>210954</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>272327</t>
+          <t>269400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>281897</t>
+          <t>279344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334013</t>
+          <t>333159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208523</t>
+          <t>210539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261086</t>
+          <t>262791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506940</t>
+          <t>510384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>581604</t>
+          <t>583253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>140197</t>
+          <t>140325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187900</t>
+          <t>186447</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254725</t>
+          <t>255537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>309644</t>
+          <t>308979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>410153</t>
+          <t>413933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480350</t>
+          <t>484881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150627</t>
+          <t>150448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197671</t>
+          <t>194881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76579</t>
+          <t>75346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>113397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234001</t>
+          <t>235139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>294247</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240266</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>292516</t>
+          <t>292437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198649</t>
+          <t>197873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>249354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>454448</t>
+          <t>452304</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526539</t>
+          <t>525185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>105966</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145692</t>
+          <t>144919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>305950</t>
+          <t>307725</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>345704</t>
+          <t>347586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>421613</t>
+          <t>424774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>483644</t>
+          <t>487137</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>127572</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170455</t>
+          <t>167552</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>67771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174351</t>
+          <t>173689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226879</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>129967</t>
+          <t>130751</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>171538</t>
+          <t>173096</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>84060</t>
+          <t>82974</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>187956</t>
+          <t>189872</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>244043</t>
+          <t>243814</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>71922</t>
+          <t>71996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104320</t>
+          <t>104734</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>311170</t>
+          <t>311293</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>333435</t>
+          <t>333653</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>384111</t>
+          <t>386530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>437488</t>
+          <t>435980</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>152647</t>
+          <t>153490</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189128</t>
+          <t>189578</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>158499</t>
+          <t>158374</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>208469</t>
+          <t>205664</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>88329</t>
+          <t>87617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>95177</t>
+          <t>95040</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>369265</t>
+          <t>369667</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>383883</t>
+          <t>384013</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>429745</t>
+          <t>431575</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>478348</t>
+          <t>481291</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>126285</t>
+          <t>125944</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>160462</t>
+          <t>158559</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>127128</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>174166</t>
+          <t>173515</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34108</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1174886</t>
+          <t>1175351</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1295126</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2127896</t>
+          <t>2125703</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2245641</t>
+          <t>2244080</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3339155</t>
+          <t>3330702</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3508414</t>
+          <t>3507018</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>787449</t>
+          <t>790521</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>889698</t>
+          <t>897288</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>355637</t>
+          <t>356689</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>430250</t>
+          <t>432704</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1170752</t>
+          <t>1168450</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1299146</t>
+          <t>1294079</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>116998</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>91729</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>145511</t>
+          <t>145453</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>199524</t>
+          <t>200753</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1208657</t>
+          <t>1198658</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1318921</t>
+          <t>1311748</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>846545</t>
+          <t>845238</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>954179</t>
+          <t>955866</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2085102</t>
+          <t>2086356</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2241909</t>
+          <t>2242424</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242974</t>
+          <t>243508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>283132</t>
+          <t>282756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>250559</t>
+          <t>249862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285880</t>
+          <t>286649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>505041</t>
+          <t>505248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>559899</t>
+          <t>560798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113466</t>
+          <t>114644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153022</t>
+          <t>153916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112020</t>
+          <t>111676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201733</t>
+          <t>199705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255364</t>
+          <t>252942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>246305</t>
+          <t>248377</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>294501</t>
+          <t>298142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263586</t>
+          <t>264316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309540</t>
+          <t>310893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>528553</t>
+          <t>525789</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>593573</t>
+          <t>592787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64347</t>
+          <t>63274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>76725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90133</t>
+          <t>90756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128575</t>
+          <t>130772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40844</t>
+          <t>40287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67754</t>
+          <t>68759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215339</t>
+          <t>215225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262885</t>
+          <t>265134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168796</t>
+          <t>168296</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>213330</t>
+          <t>212794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>398895</t>
+          <t>396852</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>462144</t>
+          <t>463368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288958</t>
+          <t>287869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342064</t>
+          <t>341097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316182</t>
+          <t>316649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366497</t>
+          <t>365596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617319</t>
+          <t>618314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691344</t>
+          <t>695163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11529,12 +11529,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>68666</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104063</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>80044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>116648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160919</t>
+          <t>159080</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212332</t>
+          <t>209513</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221461</t>
+          <t>223394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>274592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184908</t>
+          <t>187652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>233602</t>
+          <t>233957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420379</t>
+          <t>422642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>490413</t>
+          <t>493290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213682</t>
+          <t>210951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>262412</t>
+          <t>264960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>290819</t>
+          <t>288710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339346</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>516523</t>
+          <t>514212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>590369</t>
+          <t>586098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111307</t>
+          <t>111618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154402</t>
+          <t>152696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82721</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>120604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204517</t>
+          <t>206377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261660</t>
+          <t>260147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>241423</t>
+          <t>242752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>295637</t>
+          <t>295686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193504</t>
+          <t>189757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239615</t>
+          <t>239810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448616</t>
+          <t>449322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520140</t>
+          <t>521932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148631</t>
+          <t>150711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>193751</t>
+          <t>192054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>290860</t>
+          <t>289617</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>335220</t>
+          <t>334137</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>451515</t>
+          <t>450045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>516207</t>
+          <t>515493</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139370</t>
+          <t>139900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180395</t>
+          <t>184652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87611</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>199570</t>
+          <t>200352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257241</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117309</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>159105</t>
+          <t>157269</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>126966</t>
+          <t>126182</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>218898</t>
+          <t>215626</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>273471</t>
+          <t>275310</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -13151,12 +13151,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117837</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152263</t>
+          <t>151408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>300848</t>
+          <t>301278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>330712</t>
+          <t>331039</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>422968</t>
+          <t>421098</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>476280</t>
+          <t>473676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>125024</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159711</t>
+          <t>161659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151316</t>
+          <t>151478</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196677</t>
+          <t>195831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -13377,12 +13377,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>64805</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>62709</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>98672</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -13720,12 +13720,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95902</t>
+          <t>96030</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>123960</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>375845</t>
+          <t>376489</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>393109</t>
+          <t>393191</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13770,12 +13770,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>474401</t>
+          <t>473386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>516957</t>
+          <t>516481</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13805,12 +13805,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13833,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>107838</t>
+          <t>106719</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>135255</t>
+          <t>134756</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>106505</t>
+          <t>106896</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>144497</t>
+          <t>147999</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1442904</t>
+          <t>1444112</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1559712</t>
+          <t>1557913</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2173783</t>
+          <t>2164458</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2283747</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3647684</t>
+          <t>3646447</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3820062</t>
+          <t>3819124</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>654103</t>
+          <t>646471</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>747566</t>
+          <t>742836</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1022622</t>
+          <t>1024460</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1149943</t>
+          <t>1147058</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>76616</t>
+          <t>75516</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>113295</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>196425</t>
+          <t>194902</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1038811</t>
+          <t>1047905</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1152918</t>
+          <t>1151993</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>797859</t>
+          <t>800513</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>901243</t>
+          <t>906500</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1866753</t>
+          <t>1869301</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2020665</t>
+          <t>2022766</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
